--- a/Stats Sheet/Round Gaps/Moonlight.xlsx
+++ b/Stats Sheet/Round Gaps/Moonlight.xlsx
@@ -28,6 +28,9 @@
     <x:t>4</x:t>
   </x:si>
   <x:si>
+    <x:t>5</x:t>
+  </x:si>
+  <x:si>
     <x:t>_1mmortal_</x:t>
   </x:si>
   <x:si>
@@ -58,6 +61,9 @@
     <x:t>IrishandProud</x:t>
   </x:si>
   <x:si>
+    <x:t>352</x:t>
+  </x:si>
+  <x:si>
     <x:t>ItsShqky</x:t>
   </x:si>
   <x:si>
@@ -79,6 +85,9 @@
     <x:t>Ninetals38</x:t>
   </x:si>
   <x:si>
+    <x:t>428</x:t>
+  </x:si>
+  <x:si>
     <x:t>rae0vr</x:t>
   </x:si>
   <x:si>
@@ -91,6 +100,9 @@
     <x:t>Blind4ndD34f</x:t>
   </x:si>
   <x:si>
+    <x:t>220</x:t>
+  </x:si>
+  <x:si>
     <x:t>BoltsInCharge</x:t>
   </x:si>
   <x:si>
@@ -203,6 +215,54 @@
   </x:si>
   <x:si>
     <x:t>SpaceFenix</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ADinoPlayingMC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BigJedo</x:t>
+  </x:si>
+  <x:si>
+    <x:t>brinkwhy</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CodeJoshua</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CommanderK22_</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FroztiSnowman</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ItsJustSherm</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ItzBeeZ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>m4ku</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Moonlitess</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NickPlaysGames15</x:t>
+  </x:si>
+  <x:si>
+    <x:t>poWpaH</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Qmos</x:t>
+  </x:si>
+  <x:si>
+    <x:t>St0rmplayz</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SuperToads64</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Westcraft00</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -561,10 +621,10 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:H60"/>
+  <x:dimension ref="A1:I76"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
-    <x:row r="1" spans="1:8" s="1" customFormat="1">
+    <x:row r="1" spans="1:9" s="1" customFormat="1">
       <x:c r="E1" s="1">
         <x:v>45690</x:v>
       </x:c>
@@ -577,8 +637,11 @@
       <x:c r="H1" s="1">
         <x:v>45992</x:v>
       </x:c>
-    </x:row>
-    <x:row r="2" spans="1:8">
+      <x:c r="I1" s="1">
+        <x:v>46118</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2" spans="1:9">
       <x:c r="F2" s="0">
         <x:v>76</x:v>
       </x:c>
@@ -588,8 +651,11 @@
       <x:c r="H2" s="0">
         <x:v>94</x:v>
       </x:c>
-    </x:row>
-    <x:row r="3" spans="1:8">
+      <x:c r="I2" s="0">
+        <x:v>126</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3" spans="1:9">
       <x:c r="E3" s="0" t="s">
         <x:v>0</x:v>
       </x:c>
@@ -602,13 +668,16 @@
       <x:c r="H3" s="0" t="s">
         <x:v>3</x:v>
       </x:c>
-    </x:row>
-    <x:row r="4" spans="1:8">
+      <x:c r="I3" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" spans="1:9">
       <x:c r="A4" s="0">
         <x:v>1</x:v>
       </x:c>
       <x:c r="B4" s="0" t="s">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="C4" s="0" t="s">
         <x:v>0</x:v>
@@ -617,64 +686,70 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="E4" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="5" spans="1:8">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" spans="1:9">
       <x:c r="A5" s="0">
         <x:v>2</x:v>
       </x:c>
       <x:c r="B5" s="0" t="s">
-        <x:v>6</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="C5" s="0" t="s">
         <x:v>0</x:v>
       </x:c>
       <x:c r="D5" s="0">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="E5" s="0" t="s">
-        <x:v>5</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="F5" s="0" t="s">
-        <x:v>5</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="G5" s="0" t="s">
-        <x:v>5</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="H5" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="6" spans="1:8">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="I5" s="0" t="s">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" spans="1:9">
       <x:c r="A6" s="0">
         <x:v>3</x:v>
       </x:c>
       <x:c r="B6" s="0" t="s">
-        <x:v>7</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C6" s="0" t="s">
         <x:v>0</x:v>
       </x:c>
       <x:c r="D6" s="0">
-        <x:v>3</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="E6" s="0" t="s">
-        <x:v>5</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="F6" s="0" t="s">
-        <x:v>5</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="H6" s="0" t="s">
-        <x:v>8</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="7" spans="1:8">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="I6" s="0" t="s">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" spans="1:9">
       <x:c r="A7" s="0">
         <x:v>4</x:v>
       </x:c>
       <x:c r="B7" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C7" s="0" t="s">
         <x:v>0</x:v>
@@ -683,15 +758,15 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="E7" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="8" spans="1:8">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" spans="1:9">
       <x:c r="A8" s="0">
         <x:v>5</x:v>
       </x:c>
       <x:c r="B8" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C8" s="0" t="s">
         <x:v>0</x:v>
@@ -700,139 +775,154 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="E8" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9" spans="1:8">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" spans="1:9">
       <x:c r="A9" s="0">
         <x:v>6</x:v>
       </x:c>
       <x:c r="B9" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C9" s="0" t="s">
         <x:v>0</x:v>
       </x:c>
       <x:c r="D9" s="0">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="E9" s="0" t="s">
-        <x:v>5</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="F9" s="0" t="s">
-        <x:v>5</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="G9" s="0" t="s">
-        <x:v>5</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="H9" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10" spans="1:8">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="I9" s="0" t="s">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" spans="1:9">
       <x:c r="A10" s="0">
         <x:v>7</x:v>
       </x:c>
       <x:c r="B10" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="C10" s="0" t="s">
         <x:v>0</x:v>
       </x:c>
       <x:c r="D10" s="0">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="E10" s="0" t="s">
-        <x:v>5</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="F10" s="0" t="s">
-        <x:v>5</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="G10" s="0" t="s">
-        <x:v>5</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="H10" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11" spans="1:8">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="I10" s="0" t="s">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" spans="1:9">
       <x:c r="A11" s="0">
         <x:v>8</x:v>
       </x:c>
       <x:c r="B11" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C11" s="0" t="s">
         <x:v>0</x:v>
       </x:c>
       <x:c r="D11" s="0">
-        <x:v>2</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="E11" s="0" t="s">
-        <x:v>5</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="F11" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="12" spans="1:8">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="I11" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" spans="1:9">
       <x:c r="A12" s="0">
         <x:v>9</x:v>
       </x:c>
       <x:c r="B12" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C12" s="0" t="s">
         <x:v>0</x:v>
       </x:c>
       <x:c r="D12" s="0">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="E12" s="0" t="s">
-        <x:v>5</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="F12" s="0" t="s">
-        <x:v>5</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="G12" s="0" t="s">
-        <x:v>5</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="H12" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="13" spans="1:8">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="I12" s="0" t="s">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" spans="1:9">
       <x:c r="A13" s="0">
         <x:v>10</x:v>
       </x:c>
       <x:c r="B13" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="C13" s="0" t="s">
         <x:v>0</x:v>
       </x:c>
       <x:c r="D13" s="0">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="E13" s="0" t="s">
-        <x:v>5</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="F13" s="0" t="s">
-        <x:v>5</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="G13" s="0" t="s">
-        <x:v>5</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="H13" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="14" spans="1:8">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="I13" s="0" t="s">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" spans="1:9">
       <x:c r="A14" s="0">
         <x:v>11</x:v>
       </x:c>
       <x:c r="B14" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C14" s="0" t="s">
         <x:v>0</x:v>
@@ -841,41 +931,44 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="E14" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="15" spans="1:8">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" spans="1:9">
       <x:c r="A15" s="0">
         <x:v>12</x:v>
       </x:c>
       <x:c r="B15" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C15" s="0" t="s">
         <x:v>0</x:v>
       </x:c>
       <x:c r="D15" s="0">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="E15" s="0" t="s">
-        <x:v>5</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="F15" s="0" t="s">
-        <x:v>5</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="G15" s="0" t="s">
-        <x:v>5</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="H15" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="16" spans="1:8">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="I15" s="0" t="s">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" spans="1:9">
       <x:c r="A16" s="0">
         <x:v>13</x:v>
       </x:c>
       <x:c r="B16" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="C16" s="0" t="s">
         <x:v>0</x:v>
@@ -884,61 +977,67 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="E16" s="0" t="s">
-        <x:v>5</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="F16" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="17" spans="1:8">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" spans="1:9">
       <x:c r="A17" s="0">
         <x:v>14</x:v>
       </x:c>
       <x:c r="B17" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C17" s="0" t="s">
         <x:v>0</x:v>
       </x:c>
       <x:c r="D17" s="0">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="E17" s="0" t="s">
-        <x:v>5</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="F17" s="0" t="s">
-        <x:v>5</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="G17" s="0" t="s">
-        <x:v>5</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="H17" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18" spans="1:8">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="I17" s="0" t="s">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" spans="1:9">
       <x:c r="A18" s="0">
         <x:v>15</x:v>
       </x:c>
       <x:c r="B18" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C18" s="0" t="s">
         <x:v>0</x:v>
       </x:c>
       <x:c r="D18" s="0">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="E18" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19" spans="1:8">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="I18" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" spans="1:9">
       <x:c r="A19" s="0">
         <x:v>16</x:v>
       </x:c>
       <x:c r="B19" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="C19" s="0" t="s">
         <x:v>0</x:v>
@@ -947,15 +1046,15 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="E19" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="20" spans="1:8">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20" spans="1:9">
       <x:c r="A20" s="0">
         <x:v>17</x:v>
       </x:c>
       <x:c r="B20" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C20" s="0" t="s">
         <x:v>0</x:v>
@@ -964,24 +1063,24 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="E20" s="0" t="s">
-        <x:v>5</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="F20" s="0" t="s">
-        <x:v>5</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="G20" s="0" t="s">
-        <x:v>5</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="H20" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="21" spans="1:8">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21" spans="1:9">
       <x:c r="A21" s="0">
         <x:v>18</x:v>
       </x:c>
       <x:c r="B21" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C21" s="0" t="s">
         <x:v>1</x:v>
@@ -990,38 +1089,41 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="F21" s="0" t="s">
-        <x:v>5</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="G21" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="22" spans="1:8">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22" spans="1:9">
       <x:c r="A22" s="0">
         <x:v>19</x:v>
       </x:c>
       <x:c r="B22" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C22" s="0" t="s">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D22" s="0">
-        <x:v>2</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="F22" s="0" t="s">
-        <x:v>5</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="G22" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="23" spans="1:8">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="I22" s="0" t="s">
+        <x:v>28</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23" spans="1:9">
       <x:c r="A23" s="0">
         <x:v>20</x:v>
       </x:c>
       <x:c r="B23" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C23" s="0" t="s">
         <x:v>1</x:v>
@@ -1030,98 +1132,110 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="F23" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="24" spans="1:8">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24" spans="1:9">
       <x:c r="A24" s="0">
         <x:v>21</x:v>
       </x:c>
       <x:c r="B24" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C24" s="0" t="s">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D24" s="0">
-        <x:v>3</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="F24" s="0" t="s">
-        <x:v>5</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="G24" s="0" t="s">
-        <x:v>5</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="H24" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="25" spans="1:8">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="I24" s="0" t="s">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25" spans="1:9">
       <x:c r="A25" s="0">
         <x:v>22</x:v>
       </x:c>
       <x:c r="B25" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C25" s="0" t="s">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D25" s="0">
-        <x:v>2</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="F25" s="0" t="s">
-        <x:v>5</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="G25" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="26" spans="1:8">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="I25" s="0" t="s">
+        <x:v>28</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26" spans="1:9">
       <x:c r="A26" s="0">
         <x:v>23</x:v>
       </x:c>
       <x:c r="B26" s="0" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="C26" s="0" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D26" s="0">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="F26" s="0" t="s">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="G26" s="0" t="s">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="I26" s="0" t="s">
         <x:v>28</x:v>
       </x:c>
-      <x:c r="C26" s="0" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D26" s="0">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="F26" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="G26" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="27" spans="1:8">
+    </x:row>
+    <x:row r="27" spans="1:9">
       <x:c r="A27" s="0">
         <x:v>24</x:v>
       </x:c>
       <x:c r="B27" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C27" s="0" t="s">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D27" s="0">
-        <x:v>2</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="F27" s="0" t="s">
-        <x:v>5</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="G27" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="28" spans="1:8">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="I27" s="0" t="s">
+        <x:v>28</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28" spans="1:9">
       <x:c r="A28" s="0">
         <x:v>25</x:v>
       </x:c>
       <x:c r="B28" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C28" s="0" t="s">
         <x:v>1</x:v>
@@ -1130,75 +1244,84 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="F28" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="29" spans="1:8">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="29" spans="1:9">
       <x:c r="A29" s="0">
         <x:v>26</x:v>
       </x:c>
       <x:c r="B29" s="0" t="s">
-        <x:v>31</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="C29" s="0" t="s">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D29" s="0">
-        <x:v>2</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="F29" s="0" t="s">
-        <x:v>5</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="H29" s="0" t="s">
-        <x:v>8</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="30" spans="1:8">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="I29" s="0" t="s">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="30" spans="1:9">
       <x:c r="A30" s="0">
         <x:v>27</x:v>
       </x:c>
       <x:c r="B30" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="C30" s="0" t="s">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D30" s="0">
-        <x:v>2</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="F30" s="0" t="s">
-        <x:v>5</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="H30" s="0" t="s">
-        <x:v>8</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="31" spans="1:8">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="I30" s="0" t="s">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="31" spans="1:9">
       <x:c r="A31" s="0">
         <x:v>28</x:v>
       </x:c>
       <x:c r="B31" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="C31" s="0" t="s">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D31" s="0">
-        <x:v>2</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="F31" s="0" t="s">
-        <x:v>5</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="H31" s="0" t="s">
-        <x:v>8</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="32" spans="1:8">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="I31" s="0" t="s">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="32" spans="1:9">
       <x:c r="A32" s="0">
         <x:v>29</x:v>
       </x:c>
       <x:c r="B32" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C32" s="0" t="s">
         <x:v>1</x:v>
@@ -1207,38 +1330,41 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="F32" s="0" t="s">
-        <x:v>5</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="G32" s="0" t="s">
-        <x:v>5</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="H32" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="33" spans="1:8">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="33" spans="1:9">
       <x:c r="A33" s="0">
         <x:v>30</x:v>
       </x:c>
       <x:c r="B33" s="0" t="s">
-        <x:v>35</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="C33" s="0" t="s">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D33" s="0">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="F33" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="34" spans="1:8">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="I33" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="34" spans="1:9">
       <x:c r="A34" s="0">
         <x:v>31</x:v>
       </x:c>
       <x:c r="B34" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C34" s="0" t="s">
         <x:v>2</x:v>
@@ -1247,35 +1373,38 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="G34" s="0" t="s">
-        <x:v>5</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="H34" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="35" spans="1:8">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="35" spans="1:9">
       <x:c r="A35" s="0">
         <x:v>32</x:v>
       </x:c>
       <x:c r="B35" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="C35" s="0" t="s">
         <x:v>2</x:v>
       </x:c>
       <x:c r="D35" s="0">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="G35" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="36" spans="1:8">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="I35" s="0" t="s">
+        <x:v>28</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="36" spans="1:9">
       <x:c r="A36" s="0">
         <x:v>33</x:v>
       </x:c>
       <x:c r="B36" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="C36" s="0" t="s">
         <x:v>2</x:v>
@@ -1284,32 +1413,35 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="G36" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="37" spans="1:8">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="37" spans="1:9">
       <x:c r="A37" s="0">
         <x:v>34</x:v>
       </x:c>
       <x:c r="B37" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="C37" s="0" t="s">
         <x:v>2</x:v>
       </x:c>
       <x:c r="D37" s="0">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="G37" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="38" spans="1:8">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="I37" s="0" t="s">
+        <x:v>28</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="38" spans="1:9">
       <x:c r="A38" s="0">
         <x:v>35</x:v>
       </x:c>
       <x:c r="B38" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="C38" s="0" t="s">
         <x:v>2</x:v>
@@ -1318,15 +1450,15 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="G38" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="39" spans="1:8">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="39" spans="1:9">
       <x:c r="A39" s="0">
         <x:v>36</x:v>
       </x:c>
       <x:c r="B39" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="C39" s="0" t="s">
         <x:v>2</x:v>
@@ -1335,15 +1467,15 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="G39" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="40" spans="1:8">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="40" spans="1:9">
       <x:c r="A40" s="0">
         <x:v>37</x:v>
       </x:c>
       <x:c r="B40" s="0" t="s">
-        <x:v>42</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="C40" s="0" t="s">
         <x:v>2</x:v>
@@ -1352,35 +1484,38 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="G40" s="0" t="s">
-        <x:v>5</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="H40" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="41" spans="1:8">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="41" spans="1:9">
       <x:c r="A41" s="0">
         <x:v>38</x:v>
       </x:c>
       <x:c r="B41" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="C41" s="0" t="s">
         <x:v>2</x:v>
       </x:c>
       <x:c r="D41" s="0">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="G41" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="42" spans="1:8">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="I41" s="0" t="s">
+        <x:v>28</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="42" spans="1:9">
       <x:c r="A42" s="0">
         <x:v>39</x:v>
       </x:c>
       <x:c r="B42" s="0" t="s">
-        <x:v>44</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="C42" s="0" t="s">
         <x:v>3</x:v>
@@ -1389,15 +1524,15 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="H42" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="43" spans="1:8">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="43" spans="1:9">
       <x:c r="A43" s="0">
         <x:v>40</x:v>
       </x:c>
       <x:c r="B43" s="0" t="s">
-        <x:v>45</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="C43" s="0" t="s">
         <x:v>3</x:v>
@@ -1406,32 +1541,35 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="H43" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="44" spans="1:8">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="44" spans="1:9">
       <x:c r="A44" s="0">
         <x:v>41</x:v>
       </x:c>
       <x:c r="B44" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C44" s="0" t="s">
         <x:v>3</x:v>
       </x:c>
       <x:c r="D44" s="0">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="H44" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="45" spans="1:8">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="I44" s="0" t="s">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="45" spans="1:9">
       <x:c r="A45" s="0">
         <x:v>42</x:v>
       </x:c>
       <x:c r="B45" s="0" t="s">
-        <x:v>47</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="C45" s="0" t="s">
         <x:v>3</x:v>
@@ -1440,32 +1578,35 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="H45" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="46" spans="1:8">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="46" spans="1:9">
       <x:c r="A46" s="0">
         <x:v>43</x:v>
       </x:c>
       <x:c r="B46" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="C46" s="0" t="s">
         <x:v>3</x:v>
       </x:c>
       <x:c r="D46" s="0">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="H46" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="47" spans="1:8">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="I46" s="0" t="s">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="47" spans="1:9">
       <x:c r="A47" s="0">
         <x:v>44</x:v>
       </x:c>
       <x:c r="B47" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C47" s="0" t="s">
         <x:v>3</x:v>
@@ -1474,49 +1615,55 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="H47" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="48" spans="1:8">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="48" spans="1:9">
       <x:c r="A48" s="0">
         <x:v>45</x:v>
       </x:c>
       <x:c r="B48" s="0" t="s">
-        <x:v>50</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="C48" s="0" t="s">
         <x:v>3</x:v>
       </x:c>
       <x:c r="D48" s="0">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="H48" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="49" spans="1:8">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="I48" s="0" t="s">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="49" spans="1:9">
       <x:c r="A49" s="0">
         <x:v>46</x:v>
       </x:c>
       <x:c r="B49" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="C49" s="0" t="s">
         <x:v>3</x:v>
       </x:c>
       <x:c r="D49" s="0">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="H49" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="50" spans="1:8">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="I49" s="0" t="s">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="50" spans="1:9">
       <x:c r="A50" s="0">
         <x:v>47</x:v>
       </x:c>
       <x:c r="B50" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="C50" s="0" t="s">
         <x:v>3</x:v>
@@ -1525,100 +1672,115 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="H50" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="51" spans="1:8">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="51" spans="1:9">
       <x:c r="A51" s="0">
         <x:v>48</x:v>
       </x:c>
       <x:c r="B51" s="0" t="s">
-        <x:v>53</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="C51" s="0" t="s">
         <x:v>3</x:v>
       </x:c>
       <x:c r="D51" s="0">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="H51" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="52" spans="1:8">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="I51" s="0" t="s">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="52" spans="1:9">
       <x:c r="A52" s="0">
         <x:v>49</x:v>
       </x:c>
       <x:c r="B52" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="C52" s="0" t="s">
         <x:v>3</x:v>
       </x:c>
       <x:c r="D52" s="0">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="H52" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="53" spans="1:8">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="I52" s="0" t="s">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="53" spans="1:9">
       <x:c r="A53" s="0">
         <x:v>50</x:v>
       </x:c>
       <x:c r="B53" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="C53" s="0" t="s">
         <x:v>3</x:v>
       </x:c>
       <x:c r="D53" s="0">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="H53" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="54" spans="1:8">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="I53" s="0" t="s">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="54" spans="1:9">
       <x:c r="A54" s="0">
         <x:v>51</x:v>
       </x:c>
       <x:c r="B54" s="0" t="s">
-        <x:v>56</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="C54" s="0" t="s">
         <x:v>3</x:v>
       </x:c>
       <x:c r="D54" s="0">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="H54" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="55" spans="1:8">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="I54" s="0" t="s">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="55" spans="1:9">
       <x:c r="A55" s="0">
         <x:v>52</x:v>
       </x:c>
       <x:c r="B55" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="C55" s="0" t="s">
         <x:v>3</x:v>
       </x:c>
       <x:c r="D55" s="0">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="H55" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="56" spans="1:8">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="I55" s="0" t="s">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="56" spans="1:9">
       <x:c r="A56" s="0">
         <x:v>53</x:v>
       </x:c>
       <x:c r="B56" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="C56" s="0" t="s">
         <x:v>3</x:v>
@@ -1627,15 +1789,15 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="H56" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="57" spans="1:8">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="57" spans="1:9">
       <x:c r="A57" s="0">
         <x:v>54</x:v>
       </x:c>
       <x:c r="B57" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="C57" s="0" t="s">
         <x:v>3</x:v>
@@ -1644,32 +1806,35 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="H57" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="58" spans="1:8">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="58" spans="1:9">
       <x:c r="A58" s="0">
         <x:v>55</x:v>
       </x:c>
       <x:c r="B58" s="0" t="s">
-        <x:v>60</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="C58" s="0" t="s">
         <x:v>3</x:v>
       </x:c>
       <x:c r="D58" s="0">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="H58" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="59" spans="1:8">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="I58" s="0" t="s">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="59" spans="1:9">
       <x:c r="A59" s="0">
         <x:v>56</x:v>
       </x:c>
       <x:c r="B59" s="0" t="s">
-        <x:v>61</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="C59" s="0" t="s">
         <x:v>3</x:v>
@@ -1678,24 +1843,299 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="H59" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="60" spans="1:8">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="60" spans="1:9">
       <x:c r="A60" s="0">
         <x:v>57</x:v>
       </x:c>
       <x:c r="B60" s="0" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="C60" s="0" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D60" s="0">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="H60" s="0" t="s">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="I60" s="0" t="s">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="61" spans="1:9">
+      <x:c r="A61" s="0">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="B61" s="0" t="s">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="C61" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D61" s="0">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I61" s="0" t="s">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="62" spans="1:9">
+      <x:c r="A62" s="0">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="B62" s="0" t="s">
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="C62" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D62" s="0">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I62" s="0" t="s">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="63" spans="1:9">
+      <x:c r="A63" s="0">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="B63" s="0" t="s">
+        <x:v>69</x:v>
+      </x:c>
+      <x:c r="C63" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D63" s="0">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I63" s="0" t="s">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="64" spans="1:9">
+      <x:c r="A64" s="0">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="B64" s="0" t="s">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="C64" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D64" s="0">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I64" s="0" t="s">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="65" spans="1:9">
+      <x:c r="A65" s="0">
         <x:v>62</x:v>
       </x:c>
-      <x:c r="C60" s="0" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D60" s="0">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H60" s="0" t="s">
-        <x:v>5</x:v>
+      <x:c r="B65" s="0" t="s">
+        <x:v>71</x:v>
+      </x:c>
+      <x:c r="C65" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D65" s="0">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I65" s="0" t="s">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="66" spans="1:9">
+      <x:c r="A66" s="0">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="B66" s="0" t="s">
+        <x:v>72</x:v>
+      </x:c>
+      <x:c r="C66" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D66" s="0">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I66" s="0" t="s">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="67" spans="1:9">
+      <x:c r="A67" s="0">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="B67" s="0" t="s">
+        <x:v>73</x:v>
+      </x:c>
+      <x:c r="C67" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D67" s="0">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I67" s="0" t="s">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="68" spans="1:9">
+      <x:c r="A68" s="0">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="B68" s="0" t="s">
+        <x:v>74</x:v>
+      </x:c>
+      <x:c r="C68" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D68" s="0">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I68" s="0" t="s">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="69" spans="1:9">
+      <x:c r="A69" s="0">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="B69" s="0" t="s">
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="C69" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D69" s="0">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I69" s="0" t="s">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="70" spans="1:9">
+      <x:c r="A70" s="0">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="B70" s="0" t="s">
+        <x:v>76</x:v>
+      </x:c>
+      <x:c r="C70" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D70" s="0">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I70" s="0" t="s">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="71" spans="1:9">
+      <x:c r="A71" s="0">
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="B71" s="0" t="s">
+        <x:v>77</x:v>
+      </x:c>
+      <x:c r="C71" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D71" s="0">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I71" s="0" t="s">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="72" spans="1:9">
+      <x:c r="A72" s="0">
+        <x:v>69</x:v>
+      </x:c>
+      <x:c r="B72" s="0" t="s">
+        <x:v>78</x:v>
+      </x:c>
+      <x:c r="C72" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D72" s="0">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I72" s="0" t="s">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="73" spans="1:9">
+      <x:c r="A73" s="0">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="B73" s="0" t="s">
+        <x:v>79</x:v>
+      </x:c>
+      <x:c r="C73" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D73" s="0">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I73" s="0" t="s">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="74" spans="1:9">
+      <x:c r="A74" s="0">
+        <x:v>71</x:v>
+      </x:c>
+      <x:c r="B74" s="0" t="s">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="C74" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D74" s="0">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I74" s="0" t="s">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="75" spans="1:9">
+      <x:c r="A75" s="0">
+        <x:v>72</x:v>
+      </x:c>
+      <x:c r="B75" s="0" t="s">
+        <x:v>81</x:v>
+      </x:c>
+      <x:c r="C75" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D75" s="0">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I75" s="0" t="s">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="76" spans="1:9">
+      <x:c r="A76" s="0">
+        <x:v>73</x:v>
+      </x:c>
+      <x:c r="B76" s="0" t="s">
+        <x:v>82</x:v>
+      </x:c>
+      <x:c r="C76" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D76" s="0">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I76" s="0" t="s">
+        <x:v>6</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
